--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SIGALTEC.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SIGALTEC.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>85.30929999999999</v>
+        <v>85.32550000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>82.7426</v>
+        <v>83.5808</v>
       </c>
       <c r="F2" t="n">
-        <v>2.567</v>
+        <v>1.745399999999999</v>
       </c>
       <c r="G2" t="n">
         <v>53.8975</v>
@@ -610,13 +610,13 @@
         <v>50.5287</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.9334</v>
+        <v>-6.9173</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.642099999999999</v>
+        <v>-8.804</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7087</v>
+        <v>1.8871</v>
       </c>
       <c r="V2" t="n">
         <v>34.0369</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>20.5621</v>
+        <v>14.0941</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5066</v>
+        <v>11.2247</v>
       </c>
       <c r="F3" t="n">
-        <v>4.055499999999999</v>
+        <v>2.8696</v>
       </c>
       <c r="G3" t="n">
         <v>20.7278</v>
@@ -688,13 +688,13 @@
         <v>39.3654</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9708</v>
+        <v>-2.497199999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7743</v>
+        <v>-3.5077</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1969</v>
+        <v>1.0106</v>
       </c>
       <c r="V3" t="n">
         <v>-15.4959</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. LOPEZ CAMIÑA</t>
+          <t>P. FERNÁNDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6892</v>
+        <v>6.037100000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5206000000000008</v>
+        <v>3.355199999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2098</v>
+        <v>2.682100000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.6633</v>
+        <v>20.857</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7720000000000002</v>
+        <v>20.4007</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.891299999999999</v>
+        <v>0.4558999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8404</v>
+        <v>51.1413</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3779</v>
+        <v>41.52</v>
       </c>
       <c r="L4" t="n">
-        <v>-6.218100000000001</v>
+        <v>9.620699999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8232</v>
+        <v>-30.2841</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.15</v>
+        <v>-21.1194</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6735</v>
+        <v>-9.1647</v>
       </c>
       <c r="P4" t="n">
-        <v>3.7209</v>
+        <v>-21.3476</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.2878</v>
+        <v>-70.50539999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>9.008800000000001</v>
+        <v>49.1578</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2423</v>
+        <v>-14.6388</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6555999999999997</v>
+        <v>-12.5116</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4137000000000001</v>
+        <v>-2.1273</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3891</v>
+        <v>21.1665</v>
       </c>
       <c r="W4" t="n">
-        <v>8.9518</v>
+        <v>35.2315</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5627</v>
+        <v>-14.0645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SANTORUM OTERO</t>
+          <t>B. LOPEZ CAMIÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8357</v>
+        <v>2.908399999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7439</v>
+        <v>-2.0821</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0919</v>
+        <v>4.990400000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1581</v>
+        <v>-7.6633</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0269</v>
+        <v>-0.7720000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313</v>
+        <v>-6.891299999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0408</v>
+        <v>-4.8404</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0408</v>
+        <v>1.3779</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-6.218100000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.199</v>
+        <v>-2.8232</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0677</v>
+        <v>-2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1313</v>
+        <v>-0.6735</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.7209</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-5.2878</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>9.008800000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0117</v>
+        <v>-0.5386000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>-0.9058999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1071</v>
+        <v>0.3672000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6659</v>
+        <v>7.3891</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>8.9518</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SERQUEIRA ALVAREZ</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8031</v>
+        <v>0.4147000000000003</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8729</v>
+        <v>15.2707</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06989999999999996</v>
+        <v>-14.8555</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2361</v>
+        <v>8.112699999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1942999999999999</v>
+        <v>-14.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4306</v>
+        <v>22.2649</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2371</v>
+        <v>40.0296</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1224</v>
+        <v>9.036300000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3597</v>
+        <v>30.993</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9989999999999999</v>
+        <v>-31.917</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0718</v>
+        <v>-23.189</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0709</v>
+        <v>-8.7281</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7626</v>
+        <v>16.0593</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-18.0177</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>34.0773</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3295</v>
+        <v>-10.5881</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6358</v>
+        <v>-8.1753</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6938</v>
+        <v>-2.4125</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-13.1692</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4345</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-14.6037</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.778700000000001</v>
+        <v>-0.8206000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.836200000000001</v>
+        <v>-5.007600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>5.058000000000001</v>
+        <v>4.1867</v>
       </c>
       <c r="G7" t="n">
         <v>-2.012900000000001</v>
@@ -1000,13 +1000,13 @@
         <v>31.3355</v>
       </c>
       <c r="S7" t="n">
-        <v>-7.3847</v>
+        <v>-5.4265</v>
       </c>
       <c r="T7" t="n">
-        <v>-9.092599999999999</v>
+        <v>-6.2637</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7081</v>
+        <v>0.8371000000000002</v>
       </c>
       <c r="V7" t="n">
         <v>13.0818</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FERNÁNDEZ CARBALLO</t>
+          <t>P. SERQUEIRA ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9959</v>
+        <v>-0.8729</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.7328</v>
+        <v>-1.1566</v>
       </c>
       <c r="F8" t="n">
-        <v>1.737000000000001</v>
+        <v>0.2837</v>
       </c>
       <c r="G8" t="n">
-        <v>20.857</v>
+        <v>-2.2361</v>
       </c>
       <c r="H8" t="n">
-        <v>20.4007</v>
+        <v>0.1942999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4558999999999997</v>
+        <v>-2.4306</v>
       </c>
       <c r="J8" t="n">
-        <v>51.1413</v>
+        <v>-1.2371</v>
       </c>
       <c r="K8" t="n">
-        <v>41.52</v>
+        <v>0.1224</v>
       </c>
       <c r="L8" t="n">
-        <v>9.620699999999999</v>
+        <v>-1.3597</v>
       </c>
       <c r="M8" t="n">
-        <v>-30.2841</v>
+        <v>-0.9989999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-21.1194</v>
+        <v>0.0718</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.1647</v>
+        <v>-1.0709</v>
       </c>
       <c r="P8" t="n">
-        <v>-21.3476</v>
+        <v>1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-70.50539999999999</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>49.1578</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-24.6716</v>
+        <v>-0.3994</v>
       </c>
       <c r="T8" t="n">
-        <v>-21.5994</v>
+        <v>0.08049999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.0727</v>
+        <v>-0.4798</v>
       </c>
       <c r="V8" t="n">
-        <v>21.1665</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>35.2315</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.0645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CAAMAÑO ARAGUNDE</t>
+          <t>P. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.263800000000001</v>
+        <v>-0.9159</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9501</v>
+        <v>-0.7439</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.313699999999999</v>
+        <v>-0.1721</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4746</v>
+        <v>-0.1581</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08489999999999992</v>
+        <v>-0.0269</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3898</v>
+        <v>-0.1313</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4132</v>
+        <v>0.0408</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1785</v>
+        <v>0.0408</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5917000000000002</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0616</v>
+        <v>-0.199</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2637</v>
+        <v>-0.0677</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.7981</v>
+        <v>-0.1313</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9583</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9584</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.9167</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0955</v>
+        <v>-0.0919</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.795</v>
+        <v>-0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3003</v>
+        <v>0.0269</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6522</v>
+        <v>-0.6659</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>C. CAAMAÑO ARAGUNDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.325800000000002</v>
+        <v>-4.7103</v>
       </c>
       <c r="E10" t="n">
-        <v>13.2705</v>
+        <v>-2.5837</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.5966</v>
+        <v>-2.1267</v>
       </c>
       <c r="G10" t="n">
-        <v>8.112699999999998</v>
+        <v>-3.4746</v>
       </c>
       <c r="H10" t="n">
-        <v>-14.1523</v>
+        <v>-0.08489999999999992</v>
       </c>
       <c r="I10" t="n">
-        <v>22.2649</v>
+        <v>-3.3898</v>
       </c>
       <c r="J10" t="n">
-        <v>40.0296</v>
+        <v>-0.4132</v>
       </c>
       <c r="K10" t="n">
-        <v>9.036300000000001</v>
+        <v>0.1785</v>
       </c>
       <c r="L10" t="n">
-        <v>30.993</v>
+        <v>-0.5917000000000002</v>
       </c>
       <c r="M10" t="n">
-        <v>-31.917</v>
+        <v>-3.0616</v>
       </c>
       <c r="N10" t="n">
-        <v>-23.189</v>
+        <v>-0.2637</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.7281</v>
+        <v>-2.7981</v>
       </c>
       <c r="P10" t="n">
-        <v>16.0593</v>
+        <v>1.9583</v>
       </c>
       <c r="Q10" t="n">
-        <v>-18.0177</v>
+        <v>-1.9584</v>
       </c>
       <c r="R10" t="n">
-        <v>34.0773</v>
+        <v>3.9167</v>
       </c>
       <c r="S10" t="n">
-        <v>-16.3287</v>
+        <v>-1.542</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.1753</v>
+        <v>-1.4286</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.1534</v>
+        <v>-0.1132</v>
       </c>
       <c r="V10" t="n">
-        <v>-13.1692</v>
+        <v>-1.6522</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4345</v>
+        <v>1.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.6037</v>
+        <v>-2.8688</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.177</v>
+        <v>-13.2096</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.0014</v>
+        <v>-10.2591</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.175299999999999</v>
+        <v>-2.9504</v>
       </c>
       <c r="G11" t="n">
         <v>-8.542199999999999</v>
@@ -1312,13 +1312,13 @@
         <v>12.9255</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.6396</v>
+        <v>-4.6722</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9032</v>
+        <v>-2.1607</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.7366</v>
+        <v>-2.5113</v>
       </c>
       <c r="V11" t="n">
         <v>-2.9329</v>
@@ -1345,13 +1345,13 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.91</v>
+        <v>-19.0661</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.437</v>
+        <v>-16.5076</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.472900000000001</v>
+        <v>-2.5584</v>
       </c>
       <c r="G12" t="n">
         <v>-10.6893</v>
@@ -1390,13 +1390,13 @@
         <v>16.451</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2058000000000001</v>
+        <v>-2.9502</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9991</v>
+        <v>-1.0717</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7929</v>
+        <v>-1.8784</v>
       </c>
       <c r="V12" t="n">
         <v>1.428</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-39.3699</v>
+        <v>-41.0651</v>
       </c>
       <c r="E13" t="n">
-        <v>-37.9637</v>
+        <v>-55.5161</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4065</v>
+        <v>14.4505</v>
       </c>
       <c r="G13" t="n">
-        <v>-34.3843</v>
+        <v>-25.438</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.7197</v>
+        <v>-6.5555</v>
       </c>
       <c r="I13" t="n">
-        <v>-23.6647</v>
+        <v>-18.8825</v>
       </c>
       <c r="J13" t="n">
-        <v>0.426800000000001</v>
+        <v>-18.1324</v>
       </c>
       <c r="K13" t="n">
-        <v>13.0526</v>
+        <v>2.3521</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.6256</v>
+        <v>-20.4844</v>
       </c>
       <c r="M13" t="n">
-        <v>-34.8111</v>
+        <v>-7.305800000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-23.7724</v>
+        <v>-8.907500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.0388</v>
+        <v>1.6016</v>
       </c>
       <c r="P13" t="n">
-        <v>6.854700000000001</v>
+        <v>4.1129</v>
       </c>
       <c r="Q13" t="n">
-        <v>-36.4275</v>
+        <v>-31.5313</v>
       </c>
       <c r="R13" t="n">
-        <v>43.2823</v>
+        <v>35.6442</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2737</v>
+        <v>-5.4136</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.423400000000001</v>
+        <v>-5.6222</v>
       </c>
       <c r="U13" t="n">
-        <v>6.1498</v>
+        <v>0.2086</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.566599999999999</v>
+        <v>-14.327</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4611</v>
+        <v>-0.2302000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.0277</v>
+        <v>-14.0967</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-42.7032</v>
+        <v>-41.8891</v>
       </c>
       <c r="E14" t="n">
-        <v>-55.3674</v>
+        <v>-37.9179</v>
       </c>
       <c r="F14" t="n">
-        <v>12.6643</v>
+        <v>-3.9711</v>
       </c>
       <c r="G14" t="n">
-        <v>-25.438</v>
+        <v>-34.3843</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.5555</v>
+        <v>-10.7197</v>
       </c>
       <c r="I14" t="n">
-        <v>-18.8825</v>
+        <v>-23.6647</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.1324</v>
+        <v>0.426800000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3521</v>
+        <v>13.0526</v>
       </c>
       <c r="L14" t="n">
-        <v>-20.4844</v>
+        <v>-12.6256</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.305800000000001</v>
+        <v>-34.8111</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.907500000000001</v>
+        <v>-23.7724</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6016</v>
+        <v>-11.0388</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1129</v>
+        <v>6.854700000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-31.5313</v>
+        <v>-36.4275</v>
       </c>
       <c r="R14" t="n">
-        <v>35.6442</v>
+        <v>43.2823</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.0513</v>
+        <v>-4.7929</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.473100000000001</v>
+        <v>-8.377700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.578</v>
+        <v>3.5847</v>
       </c>
       <c r="V14" t="n">
-        <v>-14.327</v>
+        <v>-9.566599999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2302000000000001</v>
+        <v>6.4611</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.0967</v>
+        <v>-16.0277</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-49.9669</v>
+        <v>-46.4563</v>
       </c>
       <c r="E15" t="n">
-        <v>-33.9677</v>
+        <v>-33.8687</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.9993</v>
+        <v>-12.5875</v>
       </c>
       <c r="G15" t="n">
         <v>-21.6123</v>
@@ -1624,13 +1624,13 @@
         <v>28.2018</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.6202</v>
+        <v>-9.1099</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.5338</v>
+        <v>-5.435</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.0864</v>
+        <v>-3.675</v>
       </c>
       <c r="V15" t="n">
         <v>-24.3517</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-58.068</v>
+        <v>-49.7939</v>
       </c>
       <c r="E16" t="n">
-        <v>-41.6503</v>
+        <v>-38.2933</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.4172</v>
+        <v>-11.5005</v>
       </c>
       <c r="G16" t="n">
         <v>-9.358700000000001</v>
@@ -1702,13 +1702,13 @@
         <v>34.0772</v>
       </c>
       <c r="S16" t="n">
-        <v>-20.1085</v>
+        <v>-11.8347</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.4849</v>
+        <v>-9.127800000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.6235</v>
+        <v>-2.7071</v>
       </c>
       <c r="V16" t="n">
         <v>-22.1372</v>
@@ -1735,22 +1735,22 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-129.6374</v>
+        <v>-110.02</v>
       </c>
       <c r="E17" t="n">
-        <v>-98.52430000000001</v>
+        <v>-90.50520000000002</v>
       </c>
       <c r="F17" t="n">
-        <v>-31.1119</v>
+        <v>-19.5138</v>
       </c>
       <c r="G17" t="n">
-        <v>-21.97479999999999</v>
+        <v>-21.9748</v>
       </c>
       <c r="H17" t="n">
         <v>-23.374</v>
       </c>
       <c r="I17" t="n">
-        <v>1.397100000000002</v>
+        <v>1.397099999999995</v>
       </c>
       <c r="J17" t="n">
         <v>210.1188</v>
@@ -1774,19 +1774,19 @@
         <v>20.5632</v>
       </c>
       <c r="Q17" t="n">
-        <v>-369.1721</v>
+        <v>-369.1721000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>389.7348000000001</v>
+        <v>389.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>-101.0295</v>
+        <v>-81.41330000000002</v>
       </c>
       <c r="T17" t="n">
-        <v>-81.44840000000001</v>
+        <v>-73.43020000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-19.5807</v>
+        <v>-7.9824</v>
       </c>
       <c r="V17" t="n">
         <v>-27.19630000000002</v>
